--- a/CB_Payroll_English_Full.xlsx
+++ b/CB_Payroll_English_Full.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CB_PAYROLL_ENGLISH" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTENING" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,10 +55,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -32719,4 +32723,3026 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHU_DE</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TITLE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SCRIPT_EN</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SCRIPT_VI</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q1_A</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Q1_B</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Q1_C</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Q1_ANSWER</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_A</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_B</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_C</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_ANSWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1-Payroll</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về lịch chạy lương</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>A: Hi, I have a question about this month's payroll.
+B: Sure, go ahead. What would you like to know?
+A: When exactly is payroll processed each month?
+B: We process payroll on the 25th, based on the previous month's attendance.
+A: And when do employees actually receive their salary?
+B: Salary is transferred to their bank accounts on the 5th of the following month.
+A: What if there's an error in the attendance data?
+B: We ask the department to confirm corrections before the 20th, so we can adjust before finalizing.
+A: Do employees receive a payslip after each cycle?
+B: Yes, payslips are sent by email on the same day the salary is paid.
+A: That's very clear, thank you for explaining the whole cycle.
+B: You're welcome. Let me know if the client has any further questions.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>A: Chào anh, tôi có một câu hỏi về bảng lương tháng này.
+B: Được, chị cứ hỏi. Chị muốn biết điều gì?
+A: Chính xác thì bảng lương được xử lý vào ngày nào mỗi tháng?
+B: Chúng tôi xử lý lương vào ngày 25, dựa trên dữ liệu chấm công tháng trước.
+A: Vậy khi nào nhân viên thực sự nhận được lương?
+B: Lương được chuyển vào tài khoản ngân hàng của họ vào ngày 5 tháng sau.
+A: Nếu có sai sót trong dữ liệu chấm công thì sao?
+B: Chúng tôi yêu cầu bộ phận xác nhận điều chỉnh trước ngày 20, để có thể sửa trước khi chốt lương.
+A: Nhân viên có nhận được phiếu lương sau mỗi kỳ không?
+B: Có, phiếu lương được gửi qua email vào đúng ngày trả lương.
+A: Rất rõ ràng, cảm ơn anh đã giải thích toàn bộ quy trình.
+B: Không có gì. Nếu khách hàng có thêm câu hỏi thì chị cứ báo tôi.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Payroll is processed on which day of the month?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>The 5th</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>The 20th</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>The 25th</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>What must be confirmed before the 20th?</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Bank account details</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Attendance corrections</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Payslip format</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2-Salary</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu về cơ cấu lương</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Let me walk you through how our salary structure works.
+Every position is assigned to one of five job grades.
+Each grade has a minimum, a midpoint, and a maximum salary range.
+Gross salary includes the basic salary plus fixed allowances.
+Net salary is what the employee receives after deductions.
+We benchmark our salary ranges against the market once a year.
+Salary increases usually take effect in January.
+Any adjustment must follow the company's compensation policy.
+New hires are placed based on experience and the job grade.
+We recommend reviewing the salary structure once a year to stay competitive.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi trình bày cách cơ cấu lương của chúng ta hoạt động.
+Mỗi vị trí được xếp vào một trong năm bậc chức danh.
+Mỗi bậc có mức lương tối thiểu, trung bình và tối đa.
+Lương gộp bao gồm lương cơ bản cộng các khoản phụ cấp cố định.
+Lương thực nhận là số tiền nhân viên nhận được sau khi trừ các khoản.
+Chúng tôi so sánh mức lương với thị trường mỗi năm một lần.
+Việc tăng lương thường có hiệu lực từ tháng Một.
+Mọi điều chỉnh phải tuân theo chính sách lương của công ty.
+Nhân viên mới được xếp lương dựa trên kinh nghiệm và bậc chức danh.
+Chúng tôi khuyên nên rà soát cơ cấu lương mỗi năm để duy trì tính cạnh tranh.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>How many job grades does the structure have?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Ten</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>When do salary increases usually take effect?</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3-Allowances</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tư vấn chính sách phụ cấp</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>A: Could you clarify which allowances our company can offer?
+B: Sure. The most common ones are meal, transportation, and phone allowances.
+A: Are all of these allowances tax-exempt?
+B: No, some are taxable while others are exempt up to a certain cap.
+A: What about the housing allowance?
+B: The housing allowance is capped at a fixed amount and requires supporting documents.
+A: Do allowance rates vary by employee position?
+B: Yes, rates depend on the employee's position and department.
+A: I suggest standardizing the allowance policy across departments.
+B: That's a good idea, it would make the policy easier for employees to understand.
+A: Let's prepare a proposal and clarify which allowances are taxable.
+B: Agreed, I'll draft it and send it for your review by Friday.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể làm rõ công ty tôi có thể cấp những khoản phụ cấp nào không?
+B: Được. Phổ biến nhất là phụ cấp ăn trưa, đi lại và điện thoại.
+A: Tất cả các khoản phụ cấp này có được miễn thuế không?
+B: Không, một số phải chịu thuế, một số được miễn thuế trong một mức trần nhất định.
+A: Còn phụ cấp nhà ở thì sao?
+B: Phụ cấp nhà ở bị giới hạn ở một mức cố định và cần có chứng từ.
+A: Mức phụ cấp có thay đổi theo vị trí nhân viên không?
+B: Có, mức phụ cấp phụ thuộc vào vị trí và phòng ban của nhân viên.
+A: Tôi đề xuất chuẩn hóa chính sách phụ cấp giữa các phòng ban.
+B: Đó là một ý hay, sẽ giúp chính sách dễ hiểu hơn với nhân viên.
+A: Hãy chuẩn bị một đề xuất và làm rõ khoản nào chịu thuế.
+B: Đồng ý, tôi sẽ soạn thảo và gửi chị xem trước thứ Sáu.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Which allowance requires supporting documents?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Meal allowance</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Phone allowance</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Housing allowance</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>What does the proposal aim to clarify?</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Which allowances are taxable</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Employee bank accounts</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Working hours</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4-Deductions</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Giải thích các khoản khấu trừ trên lương</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain the deductions listed on your payslip.
+Mandatory deductions include social insurance and personal income tax.
+Social insurance is deducted directly from your gross salary.
+We deduct 10.5% in total for social, health, and unemployment insurance.
+Personal income tax is withheld monthly based on the progressive tax table.
+If you are a union member, the union fee is also deducted directly.
+All deductions are itemized clearly on your monthly payslip.
+Please double check your deductions and contact HR if anything looks unusual.
+Any unauthorized deduction must be reported immediately.
+We review the deduction process regularly to keep it transparent.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích các khoản khấu trừ trên phiếu lương của bạn.
+Các khoản khấu trừ bắt buộc gồm bảo hiểm xã hội và thuế thu nhập cá nhân.
+Bảo hiểm xã hội được khấu trừ trực tiếp từ lương gộp của bạn.
+Chúng tôi khấu trừ tổng cộng 10.5% cho bảo hiểm xã hội, y tế và thất nghiệp.
+Thuế thu nhập cá nhân được khấu trừ hàng tháng theo biểu thuế lũy tiến.
+Nếu bạn là đoàn viên công đoàn, phí công đoàn cũng được khấu trừ trực tiếp.
+Tất cả các khoản khấu trừ được liệt kê rõ ràng trên phiếu lương hàng tháng.
+Vui lòng kiểm tra kỹ các khoản khấu trừ và liên hệ HR nếu có gì bất thường.
+Bất kỳ khoản khấu trừ không hợp lệ nào cũng phải được báo cáo ngay.
+Chúng tôi rà soát quy trình khấu trừ thường xuyên để đảm bảo minh bạch.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>What percentage is deducted for social, health, and unemployment insurance combined?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>What should an employee do if a deduction looks unusual?</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Ignore it</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Contact HR</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Wait until next month</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5-Overtime</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về quy định làm thêm giờ</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>A: Can you explain how overtime pay is calculated here?
+B: Sure. Overtime pay is 150% of the normal hourly rate on weekdays.
+A: What about overtime on weekends?
+B: Weekend overtime is paid at 200%, and public holidays are paid at 300%.
+A: Do employees need approval before working overtime?
+B: Yes, overtime must be approved by the direct manager in advance.
+A: How do you track the actual overtime hours?
+B: We track overtime through the timekeeping system automatically.
+A: Is there a legal limit on how many hours someone can work overtime?
+B: Yes, excessive overtime may violate labor regulations, so we monitor it closely.
+A: I recommend reviewing the overtime approval process for our client.
+B: Agreed, that would help reduce compliance risks going forward.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể giải thích cách tính lương làm thêm giờ ở đây không?
+B: Được. Lương làm thêm giờ bằng 150% mức lương giờ bình thường vào ngày thường.
+A: Còn làm thêm giờ vào cuối tuần thì sao?
+B: Làm thêm cuối tuần được trả 200%, còn ngày lễ được trả 300%.
+A: Nhân viên có cần được phê duyệt trước khi làm thêm giờ không?
+B: Có, làm thêm giờ phải được quản lý trực tiếp phê duyệt trước.
+A: Các anh theo dõi số giờ làm thêm thực tế bằng cách nào?
+B: Chúng tôi theo dõi giờ làm thêm tự động qua hệ thống chấm công.
+A: Có giới hạn pháp lý về số giờ làm thêm không?
+B: Có, làm thêm quá mức có thể vi phạm quy định lao động nên chúng tôi giám sát chặt chẽ.
+A: Tôi đề xuất rà soát lại quy trình phê duyệt làm thêm giờ cho khách hàng.
+B: Đồng ý, điều đó sẽ giúp giảm rủi ro tuân thủ về sau.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>What is the overtime rate on public holidays?</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>200%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>300%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Who must approve overtime in advance?</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>The direct manager</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>The accounting team</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>The client</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6-Working Hours</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu chính sách giờ làm việc</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain our standard working hours policy.
+Standard working hours are eight hours a day, five days a week.
+Employees must clock in and out every day using the fingerprint scanner.
+Flexible working hours are available for certain departments.
+We monitor working hours to ensure compliance with labor law.
+Late arrivals are automatically recorded in the system.
+Break time is not counted as part of the official working hours.
+Some positions may follow a shift schedule instead of fixed hours.
+We advise adopting flexible hours whenever possible to improve satisfaction.
+The updated working hours policy will take effect next month.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích chính sách giờ làm việc tiêu chuẩn của chúng tôi.
+Giờ làm việc tiêu chuẩn là tám tiếng mỗi ngày, năm ngày mỗi tuần.
+Nhân viên phải chấm công vào ra mỗi ngày bằng máy quét vân tay.
+Giờ làm việc linh hoạt được áp dụng cho một số phòng ban.
+Chúng tôi theo dõi giờ làm việc để đảm bảo tuân thủ pháp luật lao động.
+Việc đi trễ được tự động ghi nhận trong hệ thống.
+Thời gian nghỉ giải lao không được tính vào giờ làm việc chính thức.
+Một số vị trí có thể áp dụng lịch làm việc theo ca thay vì giờ cố định.
+Chúng tôi khuyên nên áp dụng giờ linh hoạt khi có thể để cải thiện sự hài lòng.
+Chính sách giờ làm việc mới sẽ có hiệu lực từ tháng sau.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>What are the standard working hours per week?</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8 hours, 5 days</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10 hours, 4 days</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6 hours, 6 days</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Is break time counted as working hours?</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Yes, always</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Only on weekends</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7-Social Insurance</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Tư vấn về bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>A: Could you explain how social insurance contributions work?
+B: Of course. Contributions are shared between the employer and the employee.
+A: What percentage does the company pay?
+B: The company pays 17.5%, and employees contribute 8% of their salary.
+A: When must new employees be registered?
+B: New employees must be registered within the required time frame after joining.
+A: What happens if registration is delayed?
+B: Based on our experience, late registration often causes penalties.
+A: Does the social insurance book record the contribution history?
+B: Yes, it records the employee's full contribution history over time.
+A: We should update the client on the latest regulation changes.
+B: Agreed, I'll prepare a summary of the changes for tomorrow's meeting.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể giải thích cách đóng bảo hiểm xã hội hoạt động như thế nào không?
+B: Được. Khoản đóng được chia sẻ giữa người sử dụng lao động và người lao động.
+A: Công ty đóng bao nhiêu phần trăm?
+B: Công ty đóng 17.5%, còn nhân viên đóng góp 8% lương của mình.
+A: Nhân viên mới phải được đăng ký khi nào?
+B: Nhân viên mới phải được đăng ký trong thời hạn quy định sau khi vào làm.
+A: Nếu việc đăng ký bị chậm trễ thì sao?
+B: Theo kinh nghiệm của chúng tôi, đăng ký trễ thường dẫn đến bị phạt.
+A: Sổ bảo hiểm xã hội có ghi lại quá trình đóng bảo hiểm không?
+B: Có, sổ ghi lại toàn bộ quá trình đóng bảo hiểm của nhân viên theo thời gian.
+A: Chúng ta nên cập nhật cho khách hàng về những thay đổi quy định mới nhất.
+B: Đồng ý, tôi sẽ chuẩn bị bản tóm tắt các thay đổi cho cuộc họp ngày mai.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>What percentage does the employee contribute?</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>What often results from late registration?</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>A bonus</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Penalties</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>A tax refund</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8-Personal Income Tax</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Giải thích thuế thu nhập cá nhân</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain how personal income tax is calculated.
+PIT is calculated based on your taxable income each month.
+The tax rate depends on which income bracket you fall into.
+You can register dependents to reduce your taxable income.
+Tax is withheld monthly according to the progressive tax table.
+Non-resident employees are taxed at a flat rate instead.
+We issue a tax withholding certificate whenever an employee requests one.
+Each employee's tax code must be registered before their first payroll cycle.
+We advise registering dependents early to reduce taxable income sooner.
+Reviewing your tax bracket every year helps you plan your finances better.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích cách tính thuế thu nhập cá nhân.
+Thuế TNCN được tính dựa trên thu nhập chịu thuế của bạn mỗi tháng.
+Mức thuế phụ thuộc vào bậc thu nhập mà bạn thuộc vào.
+Bạn có thể đăng ký người phụ thuộc để giảm thu nhập chịu thuế.
+Thuế được khấu trừ hàng tháng theo biểu thuế lũy tiến.
+Nhân viên không cư trú bị đánh thuế theo một mức cố định.
+Chúng tôi cấp chứng từ khấu trừ thuế bất cứ khi nào nhân viên yêu cầu.
+Mã số thuế của mỗi nhân viên phải được đăng ký trước kỳ tính lương đầu tiên.
+Chúng tôi khuyên nên đăng ký người phụ thuộc sớm để giảm thu nhập chịu thuế sớm hơn.
+Việc rà soát bậc thuế mỗi năm giúp bạn hoạch định tài chính tốt hơn.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>What can employees register to reduce their taxable income?</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Dependents</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Bank accounts</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>How are non-resident employees taxed?</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Progressive tax table</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>A flat rate</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>They are not taxed</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9-PIT Finalization</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về quyết toán thuế TNCN</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>A: Could you walk me through the PIT finalization process?
+B: Sure. PIT finalization is an annual process to reconcile tax paid versus tax owed.
+A: When is the deadline for finalization each year?
+B: The deadline is usually the end of March, three months after the tax year ends.
+A: Who is responsible for finalizing tax on behalf of employees?
+B: The company can finalize on their behalf if they authorize it in writing.
+A: What documents do we need to prepare?
+B: We need the annual income summary, dependent registration, and tax paid records.
+A: What happens if an employee has overpaid tax?
+B: They can request a refund or carry the amount forward to the next year.
+A: Let's prepare a checklist so clients don't miss the deadline.
+B: Good idea, I'll draft it and share it with the team today.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể trình bày quy trình quyết toán thuế TNCN không?
+B: Được. Quyết toán thuế TNCN là quy trình hàng năm để đối chiếu thuế đã nộp và thuế phải nộp.
+A: Hạn chót quyết toán hàng năm là khi nào?
+B: Hạn chót thường là cuối tháng Ba, ba tháng sau khi kết thúc năm tính thuế.
+A: Ai chịu trách nhiệm quyết toán thuế thay cho nhân viên?
+B: Công ty có thể quyết toán thay nếu nhân viên ủy quyền bằng văn bản.
+A: Chúng ta cần chuẩn bị những tài liệu gì?
+B: Chúng ta cần bảng tổng hợp thu nhập năm, hồ sơ đăng ký người phụ thuộc và chứng từ thuế đã nộp.
+A: Nếu nhân viên nộp thừa thuế thì sao?
+B: Họ có thể yêu cầu hoàn thuế hoặc chuyển số tiền đó sang năm sau.
+A: Hãy chuẩn bị một danh sách kiểm tra để khách hàng không bỏ lỡ hạn chót.
+B: Ý hay, tôi sẽ soạn thảo và chia sẻ với nhóm hôm nay.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>When is the PIT finalization deadline usually?</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>End of January</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>What can an employee do if they overpaid tax?</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Nothing can be done</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Request a refund</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Pay double next year</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10-Labor Contracts</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu các loại hợp đồng lao động</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain the types of labor contracts we use.
+There are two main types: definite-term and indefinite-term contracts.
+A definite-term contract cannot exceed thirty-six months.
+After signing twice, the next contract must be indefinite-term.
+Every contract must clearly state salary, job title, and working location.
+A probation period may apply before the official contract begins.
+Both parties must sign the contract before the employee starts working.
+Any amendment to the contract must be made in writing.
+We keep a signed copy of every contract in the employee's file.
+We recommend reviewing contract terms annually to stay compliant.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích các loại hợp đồng lao động mà chúng tôi sử dụng.
+Có hai loại chính: hợp đồng xác định thời hạn và không xác định thời hạn.
+Hợp đồng xác định thời hạn không được quá ba mươi sáu tháng.
+Sau khi ký hai lần, hợp đồng tiếp theo phải là không xác định thời hạn.
+Mọi hợp đồng phải nêu rõ mức lương, chức danh và địa điểm làm việc.
+Có thể áp dụng thời gian thử việc trước khi hợp đồng chính thức bắt đầu.
+Cả hai bên phải ký hợp đồng trước khi nhân viên bắt đầu làm việc.
+Mọi sửa đổi hợp đồng phải được thực hiện bằng văn bản.
+Chúng tôi lưu một bản hợp đồng đã ký trong hồ sơ của mỗi nhân viên.
+Chúng tôi khuyên nên rà soát điều khoản hợp đồng hàng năm để đảm bảo tuân thủ.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>What is the maximum length of a definite-term contract?</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12 months</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36 months</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60 months</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>What must every contract clearly state?</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Salary, job title, and location</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Only the salary</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>The employee's hobbies</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11-Labor Compliance</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về tuân thủ pháp luật lao động</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>A: How do we ensure our clients stay compliant with labor law?
+B: We run a compliance checklist covering contracts, insurance, and internal regulations.
+A: How often do we review this checklist?
+B: We review it quarterly, or immediately after any regulation change.
+A: What happens if a client is found non-compliant?
+B: We flag the issue and propose a corrective action plan right away.
+A: Do we also check internal labor regulations?
+B: Yes, every company with ten or more employees must register internal regulations.
+A: What about the collective labor agreement?
+B: It's optional, but we recommend it for companies with a labor union.
+A: Let's schedule a compliance review with our top five clients this quarter.
+B: Sounds good, I'll set up the calendar invites this afternoon.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>A: Chúng ta đảm bảo khách hàng tuân thủ pháp luật lao động bằng cách nào?
+B: Chúng tôi chạy một danh sách kiểm tra tuân thủ bao gồm hợp đồng, bảo hiểm và nội quy.
+A: Chúng ta rà soát danh sách này bao lâu một lần?
+B: Chúng tôi rà soát hàng quý, hoặc ngay khi có thay đổi quy định.
+A: Nếu phát hiện khách hàng không tuân thủ thì sao?
+B: Chúng tôi đánh dấu vấn đề và đề xuất kế hoạch khắc phục ngay lập tức.
+A: Chúng ta có kiểm tra nội quy lao động không?
+B: Có, mọi công ty có từ mười lao động trở lên phải đăng ký nội quy lao động.
+A: Còn thỏa ước lao động tập thể thì sao?
+B: Đây là không bắt buộc, nhưng chúng tôi khuyên nên có nếu công ty có công đoàn.
+A: Hãy lên lịch rà soát tuân thủ với năm khách hàng lớn nhất trong quý này.
+B: Được, tôi sẽ gửi lịch mời chiều nay.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>How often is the compliance checklist reviewed?</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Once every 5 years</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Who must register internal labor regulations?</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Companies with 10+ employees</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Only foreign companies</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Only companies without a union</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12-Deadlines</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nhắc nhở các hạn nộp báo cáo quan trọng</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Let me remind everyone of the key HR and payroll deadlines this month.
+Social insurance reports must be submitted by the 5th of the following month.
+Personal income tax declarations are due by the 20th every month.
+Labor usage reports are submitted twice a year, in June and December.
+PIT finalization must be completed by the end of March annually.
+Missing a deadline can lead to administrative penalties for the client.
+We set internal reminders five working days before every deadline.
+Please double check the submission status before closing each case.
+Any delay should be reported to the team lead immediately.
+Staying ahead of deadlines protects both our clients and our reputation.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi nhắc mọi người về các hạn nộp quan trọng của HR và payroll tháng này.
+Báo cáo bảo hiểm xã hội phải nộp trước ngày 5 của tháng sau.
+Tờ khai thuế thu nhập cá nhân phải nộp trước ngày 20 hàng tháng.
+Báo cáo tình hình sử dụng lao động được nộp hai lần một năm, vào tháng Sáu và tháng Mười Hai.
+Quyết toán thuế TNCN phải hoàn thành trước cuối tháng Ba hàng năm.
+Việc trễ hạn có thể dẫn đến xử phạt hành chính cho khách hàng.
+Chúng tôi đặt nhắc nhở nội bộ trước năm ngày làm việc so với mỗi hạn chót.
+Vui lòng kiểm tra kỹ tình trạng nộp báo cáo trước khi đóng từng hồ sơ.
+Bất kỳ sự chậm trễ nào cũng cần báo ngay cho trưởng nhóm.
+Chủ động trước các hạn chót giúp bảo vệ cả khách hàng và uy tín của chúng ta.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>When are social insurance reports due?</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>The 5th of the following month</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The 20th of the same month</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>End of the year</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>How many working days ahead is the internal reminder set?</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Ten</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13-Errors and Corrections</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Xử lý sai sót trong bảng lương</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>A: I noticed an error in last month's payroll report.
+B: Thanks for flagging it. Can you tell me which employee is affected?
+A: Yes, the overtime hours for one employee were entered incorrectly.
+B: I see. Let me check the timekeeping data against the payroll file.
+A: How do we usually correct an error like this?
+B: We prepare a correction memo and adjust it in the following payroll cycle.
+A: Should we inform the client about this mistake?
+B: Yes, any correction affecting salary must be confirmed in writing with the client.
+A: What can we do to prevent this kind of error in the future?
+B: We should double check the data before finalizing payroll each month.
+A: Let's also add a review step for overtime data specifically.
+B: Agreed, I'll update our checklist today.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>A: Tôi phát hiện một lỗi trong báo cáo lương tháng trước.
+B: Cảm ơn chị đã báo. Chị cho tôi biết nhân viên nào bị ảnh hưởng nhé?
+A: Vâng, số giờ làm thêm của một nhân viên đã bị nhập sai.
+B: Tôi hiểu rồi. Để tôi kiểm tra dữ liệu chấm công đối chiếu với file lương.
+A: Chúng ta thường sửa lỗi như thế này như thế nào?
+B: Chúng tôi lập biên bản điều chỉnh và sửa vào kỳ lương tiếp theo.
+A: Chúng ta có nên báo cho khách hàng về sai sót này không?
+B: Có, mọi điều chỉnh ảnh hưởng đến lương phải được xác nhận bằng văn bản với khách hàng.
+A: Chúng ta có thể làm gì để tránh lỗi này trong tương lai?
+B: Chúng ta nên kiểm tra kỹ dữ liệu trước khi chốt lương mỗi tháng.
+A: Hãy thêm một bước rà soát riêng cho dữ liệu làm thêm giờ.
+B: Đồng ý, tôi sẽ cập nhật danh sách kiểm tra ngay hôm nay.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>What was entered incorrectly in the payroll report?</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Tax code</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Bank account</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>What must be confirmed in writing with the client?</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Any correction affecting salary</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>The office address</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>The holiday schedule</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14-Meetings</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Chuẩn bị cho cuộc họp với khách hàng</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Let me walk you through how we prepare for a client meeting.
+First, we review the client's outstanding issues from the previous meeting.
+We prepare a short agenda with clear discussion points.
+All relevant payroll and compliance data must be ready beforehand.
+We share the report on screen so everyone can follow along.
+If anyone has a concern, we encourage them to raise it early.
+We summarize the key points before closing each agenda item.
+Action items are assigned with a clear deadline and owner.
+We always confirm the next follow-up meeting before ending the call.
+A short meeting summary is sent to the client within the same day.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi trình bày cách chúng tôi chuẩn bị cho một cuộc họp với khách hàng.
+Đầu tiên, chúng tôi rà soát các vấn đề còn tồn đọng từ cuộc họp trước.
+Chúng tôi chuẩn bị một chương trình họp ngắn gọn với các điểm thảo luận rõ ràng.
+Tất cả dữ liệu lương và tuân thủ liên quan phải sẵn sàng trước.
+Chúng tôi chia sẻ báo cáo lên màn hình để mọi người cùng theo dõi.
+Nếu ai có mối lo ngại, chúng tôi khuyến khích họ nêu ra sớm.
+Chúng tôi tóm tắt các điểm chính trước khi kết thúc mỗi mục trong chương trình.
+Các việc cần làm được giao với hạn chót và người phụ trách rõ ràng.
+Chúng tôi luôn xác nhận cuộc họp tiếp theo trước khi kết thúc cuộc gọi.
+Bản tóm tắt cuộc họp ngắn gọn được gửi cho khách hàng trong cùng ngày.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>What is prepared before every client meeting?</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>A short agenda</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>A new contract</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>A tax refund</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>When is the meeting summary sent to the client?</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Within the same day</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>One week later</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Only if requested</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15-Discussing Issues and Problems</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi khi phát sinh vấn đề với khách hàng</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>A: I'd like to raise a concern about this month's headcount report.
+B: Sure, what seems to be the issue?
+A: The client's headcount doesn't match what we submitted to social insurance.
+B: That's a serious issue. Let's check the source data first.
+A: I think two resignations weren't updated in time.
+B: Let's confirm with the client and correct the report as soon as possible.
+A: Should we also inform the client proactively about the delay?
+B: Yes, transparency helps us maintain trust, even when there's a mistake.
+A: What steps can we take to prevent this from happening again?
+B: We should set a monthly cross-check between HR data and insurance reports.
+A: Good idea, I'll draft a simple checklist for the team.
+B: Great, let's implement it starting next month.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>A: Tôi muốn nêu một mối lo ngại về báo cáo nhân sự tháng này.
+B: Được, vấn đề là gì vậy?
+A: Số lượng nhân sự của khách hàng không khớp với báo cáo chúng ta đã nộp bảo hiểm xã hội.
+B: Đây là vấn đề nghiêm trọng. Hãy kiểm tra dữ liệu gốc trước.
+A: Tôi nghĩ hai trường hợp nghỉ việc chưa được cập nhật kịp thời.
+B: Hãy xác nhận với khách hàng và sửa báo cáo càng sớm càng tốt.
+A: Chúng ta có nên chủ động thông báo cho khách hàng về sự chậm trễ này không?
+B: Có, sự minh bạch giúp chúng ta duy trì niềm tin, kể cả khi có sai sót.
+A: Chúng ta có thể làm gì để tránh việc này xảy ra lần nữa?
+B: Chúng ta nên đối chiếu chéo hàng tháng giữa dữ liệu HR và báo cáo bảo hiểm.
+A: Ý hay, tôi sẽ soạn một danh sách kiểm tra đơn giản cho nhóm.
+B: Tốt, hãy áp dụng từ tháng sau.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>What didn't match between reports?</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Headcount data</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Tax rates</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>What solution is proposed to prevent this issue again?</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>A monthly cross-check</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Firing the employee</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Ignoring the mismatch</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16-Conflict Resolution and Difficult Conversations</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cách xử lý tình huống khó với khách hàng</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Let me share how we approach a difficult conversation with a client.
+First, we listen carefully before responding to any complaint.
+We acknowledge the client's concern without becoming defensive.
+It's important to separate the facts from the emotions in the conversation.
+We explain our process clearly, using simple and honest language.
+If we made a mistake, we admit it and propose a concrete solution.
+We avoid making promises we cannot keep under pressure.
+A follow-up email after the conversation helps confirm what was agreed.
+We always involve our manager for escalated or sensitive cases.
+Handling conflict well often strengthens the relationship with the client.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi chia sẻ cách chúng tôi xử lý một cuộc trò chuyện khó với khách hàng.
+Đầu tiên, chúng tôi lắng nghe kỹ trước khi phản hồi bất kỳ khiếu nại nào.
+Chúng tôi ghi nhận mối lo ngại của khách hàng mà không tỏ ra phòng thủ.
+Điều quan trọng là tách biệt sự việc và cảm xúc trong cuộc trò chuyện.
+Chúng tôi giải thích quy trình một cách rõ ràng, bằng ngôn ngữ đơn giản và trung thực.
+Nếu chúng tôi mắc lỗi, chúng tôi thừa nhận và đề xuất giải pháp cụ thể.
+Chúng tôi tránh hứa hẹn những điều không thể thực hiện dưới áp lực.
+Email theo sau cuộc trò chuyện giúp xác nhận những gì đã thống nhất.
+Chúng tôi luôn có sự tham gia của quản lý cho các trường hợp nhạy cảm hoặc leo thang.
+Xử lý xung đột tốt thường giúp củng cố mối quan hệ với khách hàng.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>What should be separated during a difficult conversation?</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Facts and emotions</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Salary and bonus</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Contracts and reports</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Who is involved for escalated or sensitive cases?</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>The manager</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>The client's competitor</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>No one</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>17-Email and Written Communication</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi cách viết email chuyên nghiệp</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>A: Could you review this email before I send it to the client?
+B: Sure, let me take a look. What's the purpose of this email?
+A: I'm confirming the payroll report and asking for their approval.
+B: I'd suggest starting with a clear subject line stating the deadline.
+A: Good point, I'll add the due date right in the subject.
+B: Also, keep the body short and use bullet points for the key numbers.
+A: Should I attach the full report or just summarize it in the email?
+B: Attach the full file, but summarize the highlights in two or three lines.
+A: What's a professional way to ask them to confirm by a certain date?
+B: You could write: please confirm by Friday so we can proceed on schedule.
+A: That sounds clear and polite, thank you.
+B: No problem, always keep written communication clear and courteous.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể xem lại email này trước khi tôi gửi cho khách hàng không?
+B: Được, để tôi xem. Mục đích của email này là gì?
+A: Tôi đang xác nhận báo cáo lương và xin phê duyệt từ họ.
+B: Tôi đề xuất bắt đầu bằng tiêu đề rõ ràng nêu rõ hạn chót.
+A: Ý hay, tôi sẽ thêm ngày hạn ngay trong tiêu đề.
+B: Ngoài ra, giữ nội dung ngắn gọn và dùng gạch đầu dòng cho các số liệu chính.
+A: Tôi nên đính kèm báo cáo đầy đủ hay chỉ tóm tắt trong email?
+B: Đính kèm file đầy đủ, nhưng tóm tắt điểm nổi bật trong hai đến ba dòng.
+A: Cách viết chuyên nghiệp để yêu cầu họ xác nhận trước một ngày nhất định là gì?
+B: Chị có thể viết: vui lòng xác nhận trước thứ Sáu để chúng tôi tiến hành đúng tiến độ.
+A: Nghe rõ ràng và lịch sự, cảm ơn anh.
+B: Không có gì, hãy luôn giữ văn phong lịch sự và rõ ràng trong email.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>What should the subject line clearly state?</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>The deadline</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>The employee's name</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>The office address</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>What is recommended for presenting key numbers in the email body?</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Long paragraphs</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Bullet points</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>No numbers at all</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18-Interview (Candidate)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Phỏng vấn ứng viên</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>A: Thank you for coming in today, please have a seat.
+B: Thank you for having me, I'm excited about this opportunity.
+A: Can you briefly introduce your work experience?
+B: I've worked in HR for five years, mainly in compensation and benefits.
+A: What made you interested in this position?
+B: I'm looking for a role with more strategic responsibility in C&amp;B.
+A: Can you tell me about a challenging project you handled?
+B: I led a project to redesign the salary structure for the whole company.
+A: What is your expected salary for this role?
+B: Based on my experience, I'm expecting a competitive market rate.
+A: Do you have any questions for us?
+B: Yes, could you tell me more about the team I'd be working with?</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>A: Cảm ơn bạn đã đến hôm nay, mời bạn ngồi.
+B: Cảm ơn đã mời tôi, tôi rất hào hứng với cơ hội này.
+A: Bạn có thể giới thiệu ngắn gọn về kinh nghiệm làm việc của mình không?
+B: Tôi đã làm việc trong ngành HR năm năm, chủ yếu về lương thưởng và phúc lợi.
+A: Điều gì khiến bạn quan tâm đến vị trí này?
+B: Tôi đang tìm một vị trí có trách nhiệm mang tính chiến lược hơn về C&amp;B.
+A: Bạn có thể kể về một dự án khó khăn mà bạn từng xử lý không?
+B: Tôi đã dẫn dắt dự án thiết kế lại cơ cấu lương cho toàn công ty.
+A: Mức lương mong muốn của bạn cho vị trí này là bao nhiêu?
+B: Dựa trên kinh nghiệm của tôi, tôi mong muốn mức lương cạnh tranh theo thị trường.
+A: Bạn có câu hỏi gì cho chúng tôi không?
+B: Có, anh/chị có thể cho tôi biết thêm về đội nhóm tôi sẽ làm việc cùng không?</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>What area does the candidate have experience in?</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Compensation and benefits</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>IT support</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>What did the candidate lead a project on?</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Redesigning the salary structure</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Building a new office</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Hiring interns</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>19-Interview Feedback (Line Manager)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Phản hồi của quản lý sau phỏng vấn</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Let me share my feedback on the candidate we interviewed yesterday.
+Overall, I think the candidate has strong technical knowledge.
+Their experience in compensation and benefits matches what we need.
+However, I noticed some hesitation when discussing team management.
+I'd like to see more examples of cross-department collaboration.
+Their communication style was clear and professional throughout.
+I think we should invite them for a second round with the director.
+Their salary expectation is within our approved budget range.
+I recommend HR follow up within this week to keep them engaged.
+Overall, this is a promising candidate worth moving forward with.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi chia sẻ nhận xét của tôi về ứng viên chúng ta phỏng vấn hôm qua.
+Nhìn chung, tôi thấy ứng viên có kiến thức chuyên môn khá vững.
+Kinh nghiệm của họ về lương thưởng và phúc lợi phù hợp với nhu cầu của chúng ta.
+Tuy nhiên, tôi nhận thấy có sự do dự khi họ nói về quản lý đội nhóm.
+Tôi muốn thấy thêm ví dụ về sự phối hợp giữa các phòng ban.
+Phong cách giao tiếp của họ rõ ràng và chuyên nghiệp xuyên suốt buổi phỏng vấn.
+Tôi nghĩ chúng ta nên mời họ vào vòng phỏng vấn thứ hai với giám đốc.
+Mức lương mong muốn của họ nằm trong ngân sách đã được duyệt.
+Tôi đề xuất HR liên hệ lại trong tuần này để giữ họ quan tâm đến vị trí.
+Nhìn chung, đây là một ứng viên tiềm năng đáng để tiếp tục quy trình.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>What did the manager want to see more examples of?</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Cross-department collaboration</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Sick leave requests</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>What is the manager's recommendation?</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Invite the candidate for a second round</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Reject the candidate immediately</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Offer a lower salary</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20-Promotion</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về xét thăng chức</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>A: I'd like to discuss the promotion criteria for this year.
+B: Sure, what factors do we usually consider?
+A: We look at performance results, leadership potential, and tenure.
+B: Is there a minimum performance rating required?
+A: Yes, employees must score at least a 'meets expectations' rating.
+B: How does the promotion process actually start?
+A: The line manager submits a proposal, which HR then reviews.
+B: Does a promotion always come with a salary increase?
+A: Usually yes, based on the new job grade and market benchmark.
+B: When are promotion decisions typically finalized?
+A: Most promotions are finalized during the annual review cycle.
+B: Thanks, that clarifies the whole process for me.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>A: Tôi muốn thảo luận về tiêu chí xét thăng chức năm nay.
+B: Được, chúng ta thường xem xét những yếu tố nào?
+A: Chúng ta xem xét kết quả công việc, tiềm năng lãnh đạo và thâm niên.
+B: Có yêu cầu điểm đánh giá tối thiểu nào không?
+A: Có, nhân viên phải đạt ít nhất mức đánh giá 'đáp ứng kỳ vọng'.
+B: Quy trình thăng chức thực sự bắt đầu như thế nào?
+A: Quản lý trực tiếp nộp đề xuất, sau đó HR sẽ rà soát.
+B: Thăng chức có luôn đi kèm tăng lương không?
+A: Thường là có, dựa trên bậc chức danh mới và mức lương thị trường.
+B: Quyết định thăng chức thường được chốt vào thời điểm nào?
+A: Hầu hết các quyết định thăng chức được chốt trong kỳ đánh giá hàng năm.
+B: Cảm ơn, giờ tôi đã hiểu rõ toàn bộ quy trình.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Who submits the promotion proposal first?</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>The line manager</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>HR director</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>The employee themselves</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>When are most promotions finalized?</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>During the annual review cycle</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>On the employee's birthday</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Randomly each month</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>21-KPI</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu hệ thống chỉ số KPI</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain how our KPI system works.
+Each employee has three to five key performance indicators.
+KPIs are set at the beginning of each quarter with the line manager.
+Targets should be specific, measurable, and realistic.
+We review KPI progress at the mid-quarter check-in.
+Final results are scored on a scale from one to five.
+KPI results directly affect the quarterly bonus calculation.
+Employees can raise concerns if a target becomes unrealistic.
+HR provides a template to standardize KPI setting across departments.
+A clear KPI system helps employees understand what success looks like.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích hệ thống chỉ số KPI của chúng ta hoạt động như thế nào.
+Mỗi nhân viên có từ ba đến năm chỉ số hiệu suất chính.
+KPI được thiết lập vào đầu mỗi quý cùng với quản lý trực tiếp.
+Mục tiêu cần cụ thể, đo lường được và khả thi.
+Chúng tôi rà soát tiến độ KPI vào giữa quý.
+Kết quả cuối cùng được chấm điểm theo thang từ một đến năm.
+Kết quả KPI ảnh hưởng trực tiếp đến việc tính thưởng theo quý.
+Nhân viên có thể nêu ý kiến nếu mục tiêu trở nên không khả thi.
+HR cung cấp mẫu để chuẩn hóa việc thiết lập KPI giữa các phòng ban.
+Một hệ thống KPI rõ ràng giúp nhân viên hiểu thành công được đo lường như thế nào.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>How many KPIs does each employee typically have?</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Three to five</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Ten or more</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>What do KPI results directly affect?</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>The quarterly bonus</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>The office location</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>The lunch allowance</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22-Talent</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về chiến lược nhân tài</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>A: How does our company identify high-potential talent?
+B: We combine performance results with a potential assessment each year.
+A: What happens after someone is identified as high-potential?
+B: They're added to a talent pool with a personalized development plan.
+A: Does the company offer mentoring for these employees?
+B: Yes, each high-potential employee is paired with a senior mentor.
+A: How do we retain talent once they're identified?
+B: We offer clearer career paths and slightly faster salary progression.
+A: Is talent identification linked to succession planning?
+B: Definitely, talent pools are the main source for succession planning.
+A: This sounds like a solid long-term strategy.
+B: It is, and we review the talent pool every year to keep it updated.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>A: Công ty chúng ta xác định nhân tài tiềm năng cao như thế nào?
+B: Chúng tôi kết hợp kết quả công việc với đánh giá tiềm năng mỗi năm.
+A: Điều gì xảy ra sau khi ai đó được xác định là nhân tài tiềm năng?
+B: Họ được thêm vào nhóm nhân tài với kế hoạch phát triển riêng.
+A: Công ty có chương trình cố vấn cho những nhân viên này không?
+B: Có, mỗi nhân viên tiềm năng cao được ghép với một cố vấn cấp cao.
+A: Chúng ta giữ chân nhân tài như thế nào sau khi đã xác định?
+B: Chúng tôi đưa ra lộ trình sự nghiệp rõ ràng hơn và tăng lương nhanh hơn một chút.
+A: Việc xác định nhân tài có liên kết với kế hoạch kế nhiệm không?
+B: Chắc chắn rồi, nhóm nhân tài là nguồn chính cho kế hoạch kế nhiệm.
+A: Nghe có vẻ đây là một chiến lược dài hạn vững chắc.
+B: Đúng vậy, và chúng tôi rà soát nhóm nhân tài mỗi năm để cập nhật.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>What is each high-potential employee paired with?</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>A senior mentor</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>A new laptop</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>A second job</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>What is the main source for succession planning?</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Talent pools</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Overtime records</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Customer feedback</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>23-Compliance</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu về tuân thủ nội bộ</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain our approach to internal compliance.
+Compliance covers labor law, tax regulations, and internal policies.
+We conduct an internal audit at least once a year.
+Every new regulation is reviewed by the compliance team within a week.
+Employees receive compliance training when they join the company.
+Any violation must be reported through the internal reporting channel.
+We keep detailed records to demonstrate compliance during inspections.
+Non-compliance can result in financial penalties for the company.
+We update our compliance checklist whenever the law changes.
+A strong compliance culture protects both the company and its employees.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích cách tiếp cận của chúng ta về tuân thủ nội bộ.
+Tuân thủ bao gồm pháp luật lao động, quy định thuế và chính sách nội bộ.
+Chúng tôi thực hiện kiểm tra nội bộ ít nhất một lần mỗi năm.
+Mọi quy định mới được đội tuân thủ rà soát trong vòng một tuần.
+Nhân viên được đào tạo về tuân thủ khi gia nhập công ty.
+Bất kỳ vi phạm nào cũng phải được báo cáo qua kênh báo cáo nội bộ.
+Chúng tôi lưu hồ sơ chi tiết để chứng minh sự tuân thủ khi có thanh tra.
+Việc không tuân thủ có thể dẫn đến xử phạt tài chính cho công ty.
+Chúng tôi cập nhật danh sách kiểm tra tuân thủ mỗi khi luật thay đổi.
+Văn hóa tuân thủ vững mạnh bảo vệ cả công ty và nhân viên.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>How often is the internal audit conducted?</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>At least once a year</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Every 5 years</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>What can non-compliance result in?</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Financial penalties</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>A bonus</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>A promotion</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24-Work life Balance</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về cân bằng công việc và cuộc sống</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>A: How does the company support work-life balance?
+B: We offer flexible working hours and the option to work from home.
+A: Does the company limit overtime to protect employee wellbeing?
+B: Yes, we monitor overtime hours and flag excessive cases to managers.
+A: Are there any wellness programs available?
+B: We provide an annual health check and a small wellness allowance.
+A: How do managers encourage employees to take annual leave?
+B: HR sends a reminder if unused leave is piling up near year-end.
+A: Do employees feel comfortable raising workload concerns?
+B: We encourage open conversations between employees and managers about workload.
+A: This sounds like a genuinely supportive culture.
+B: We try, because a balanced team performs better in the long run.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>A: Công ty hỗ trợ cân bằng công việc và cuộc sống như thế nào?
+B: Chúng tôi cung cấp giờ làm việc linh hoạt và tùy chọn làm việc tại nhà.
+A: Công ty có giới hạn làm thêm giờ để bảo vệ sức khỏe nhân viên không?
+B: Có, chúng tôi theo dõi giờ làm thêm và cảnh báo các trường hợp quá mức cho quản lý.
+A: Có chương trình chăm sóc sức khỏe nào không?
+B: Chúng tôi cung cấp khám sức khỏe hàng năm và một khoản phụ cấp chăm sóc sức khỏe.
+A: Quản lý khuyến khích nhân viên nghỉ phép năm như thế nào?
+B: HR gửi nhắc nhở nếu số ngày phép chưa dùng đang tăng vào cuối năm.
+A: Nhân viên có cảm thấy thoải mái khi nêu vấn đề về khối lượng công việc không?
+B: Chúng tôi khuyến khích trao đổi cởi mở giữa nhân viên và quản lý về khối lượng công việc.
+A: Nghe có vẻ đây thực sự là một văn hóa hỗ trợ tốt.
+B: Chúng tôi cố gắng, vì một đội ngũ cân bằng sẽ làm việc hiệu quả hơn về lâu dài.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>What does the company monitor to protect wellbeing?</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Overtime hours</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Lunch orders</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>What does HR send if unused leave is piling up?</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>A reminder</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>A warning letter</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>A pay cut notice</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>25-Benefit</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu chính sách phúc lợi</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Let me introduce our employee benefits package.
+All full-time employees receive health insurance from day one.
+We also provide an annual health check-up at a partner hospital.
+Employees are entitled to twelve days of annual leave per year.
+We offer a birthday gift and a holiday bonus twice a year.
+Parental leave is available for both mothers and fathers.
+Employees can also join our optional life insurance program.
+We review the benefits package every year based on employee feedback.
+New benefits are usually announced during the annual town hall meeting.
+We believe a strong benefits package helps us attract and retain talent.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giới thiệu gói phúc lợi dành cho nhân viên.
+Tất cả nhân viên toàn thời gian được hưởng bảo hiểm sức khỏe ngay từ ngày đầu.
+Chúng tôi cũng cung cấp khám sức khỏe hàng năm tại bệnh viện đối tác.
+Nhân viên được hưởng mười hai ngày phép năm mỗi năm.
+Chúng tôi tặng quà sinh nhật và thưởng lễ hai lần mỗi năm.
+Nghỉ thai sản được áp dụng cho cả người mẹ và người cha.
+Nhân viên cũng có thể tham gia chương trình bảo hiểm nhân thọ tự nguyện.
+Chúng tôi rà soát gói phúc lợi mỗi năm dựa trên phản hồi của nhân viên.
+Các phúc lợi mới thường được công bố trong cuộc họp toàn công ty hàng năm.
+Chúng tôi tin rằng một gói phúc lợi tốt giúp thu hút và giữ chân nhân tài.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>How many days of annual leave do employees receive?</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Ten days</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Twelve days</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Twenty days</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Where are new benefits usually announced?</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>The annual town hall meeting</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>A private email</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>A newspaper ad</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>26-Salary Guide</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về báo cáo khảo sát lương</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>A: Have you seen this year's salary guide report?
+B: Yes, I reviewed it yesterday. It's quite detailed by industry.
+A: How can we use this data for our clients?
+B: We can benchmark their salary ranges against the market average.
+A: Does the report break down salary by job level?
+B: Yes, it shows entry, mid, senior, and management levels separately.
+A: Should we recommend any salary adjustment based on this data?
+B: If a client's rate falls below the market range, yes, we should flag it.
+A: How often is this salary guide updated?
+B: It's usually updated once a year, based on market survey data.
+A: Let's prepare a summary slide for our upcoming client meeting.
+B: Sure, I'll have it ready by tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh đã xem báo cáo khảo sát lương năm nay chưa?
+B: Rồi, tôi xem hôm qua. Báo cáo khá chi tiết theo từng ngành.
+A: Chúng ta có thể dùng dữ liệu này cho khách hàng như thế nào?
+B: Chúng ta có thể so sánh mức lương của họ với mức trung bình thị trường.
+A: Báo cáo có phân tách mức lương theo cấp bậc công việc không?
+B: Có, báo cáo hiển thị riêng các cấp mới vào nghề, trung cấp, cao cấp và quản lý.
+A: Chúng ta có nên đề xuất điều chỉnh lương dựa trên dữ liệu này không?
+B: Nếu mức lương của khách hàng thấp hơn khoảng thị trường, có, chúng ta nên cảnh báo.
+A: Báo cáo khảo sát lương này được cập nhật bao lâu một lần?
+B: Thường được cập nhật một lần mỗi năm, dựa trên dữ liệu khảo sát thị trường.
+A: Hãy chuẩn bị một slide tóm tắt cho cuộc họp khách hàng sắp tới.
+B: Được, tôi sẽ chuẩn bị xong trước sáng mai.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>What does the report break down by?</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Job level</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Office size</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>What should be flagged if a client's rate is below market range?</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>A salary adjustment</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>A new office</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>A holiday schedule</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>27-People Assessment</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu quy trình đánh giá nhân sự</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Let me explain how our people assessment process works.
+We assess employees twice a year, in June and December.
+The assessment covers performance results and core competencies.
+Employees first complete a self-assessment before the manager review.
+Managers then provide their own rating and written feedback.
+We use a five-point rating scale for consistency across departments.
+Results feed directly into bonus, promotion, and training decisions.
+HR calibrates ratings across teams to reduce individual bias.
+Employees can discuss their results in a one-on-one meeting.
+A fair assessment process builds trust between employees and managers.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi giải thích quy trình đánh giá nhân sự của chúng ta.
+Chúng tôi đánh giá nhân viên hai lần một năm, vào tháng Sáu và tháng Mười Hai.
+Đánh giá bao gồm kết quả công việc và năng lực cốt lõi.
+Nhân viên tự đánh giá trước khi quản lý tiến hành rà soát.
+Sau đó quản lý đưa ra đánh giá riêng và nhận xét bằng văn bản.
+Chúng tôi dùng thang điểm năm mức để đảm bảo tính nhất quán giữa các phòng ban.
+Kết quả đánh giá được dùng trực tiếp cho quyết định thưởng, thăng chức và đào tạo.
+HR hiệu chỉnh điểm đánh giá giữa các nhóm để giảm thiên vị cá nhân.
+Nhân viên có thể thảo luận về kết quả trong buổi trao đổi riêng.
+Một quy trình đánh giá công bằng giúp xây dựng niềm tin giữa nhân viên và quản lý.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>How many times a year is the assessment conducted?</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Once</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Twice</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Four times</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>What does HR do to reduce individual bias?</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Calibrate ratings across teams</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Skip the assessment</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Only assess managers</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>28-Org Chart</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về cập nhật sơ đồ tổ chức</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>A: Could you help me update the client's org chart?
+B: Sure, what changes do we need to make?
+A: Two new hires joined the finance department last week.
+B: Got it. Who do they report to?
+A: Both report directly to the finance manager.
+B: Should we also update the reporting line for the HR team?
+A: Yes, HR now reports to the general director instead of the CFO.
+B: That's a significant structural change, I'll highlight it clearly.
+A: How often do we usually review the org chart with clients?
+B: We review it quarterly, or whenever there's a major personnel change.
+A: Let's send the updated chart to the client for confirmation.
+B: Sure, I'll prepare the file and send it today.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể giúp tôi cập nhật sơ đồ tổ chức của khách hàng không?
+B: Được, chúng ta cần thay đổi những gì?
+A: Hai nhân viên mới gia nhập phòng tài chính tuần trước.
+B: Rõ rồi. Họ báo cáo cho ai?
+A: Cả hai đều báo cáo trực tiếp cho trưởng phòng tài chính.
+B: Chúng ta có cần cập nhật tuyến báo cáo của đội HR không?
+A: Có, HR giờ báo cáo cho tổng giám đốc thay vì giám đốc tài chính.
+B: Đây là một thay đổi cấu trúc đáng kể, tôi sẽ làm nổi bật rõ ràng.
+A: Chúng ta thường rà soát sơ đồ tổ chức với khách hàng bao lâu một lần?
+B: Chúng tôi rà soát hàng quý, hoặc bất cứ khi nào có thay đổi nhân sự lớn.
+A: Hãy gửi sơ đồ đã cập nhật cho khách hàng để xác nhận.
+B: Được, tôi sẽ chuẩn bị file và gửi hôm nay.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Who do the two new hires report to?</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>The finance manager</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>The HR manager</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>The client</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>How often is the org chart usually reviewed?</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Every 5 years</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>29-Structure &amp; Direction</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>monologue</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu định hướng cơ cấu tổ chức</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Let me share our thinking on organizational structure and direction.
+As the company grows, we're moving toward a more functional structure.
+Each function will have a clear head reporting to the general director.
+This structure aims to reduce overlapping responsibilities.
+We plan to review the structure again in eighteen months.
+Clear reporting lines help decisions move faster across the company.
+We're also defining clearer career paths within each function.
+This direction supports our goal of scaling to new markets.
+HR will update job descriptions to match the new structure.
+We will communicate these changes clearly to all employees.</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Để tôi chia sẻ định hướng của chúng ta về cơ cấu tổ chức.
+Khi công ty phát triển, chúng ta đang chuyển sang cơ cấu theo chức năng rõ hơn.
+Mỗi chức năng sẽ có một trưởng bộ phận báo cáo trực tiếp cho tổng giám đốc.
+Cơ cấu này nhằm giảm thiểu sự chồng chéo trách nhiệm.
+Chúng ta dự kiến rà soát lại cơ cấu này sau mười tám tháng nữa.
+Tuyến báo cáo rõ ràng giúp các quyết định được đưa ra nhanh hơn trong toàn công ty.
+Chúng ta cũng đang xác định lộ trình sự nghiệp rõ ràng hơn trong từng chức năng.
+Định hướng này hỗ trợ mục tiêu mở rộng sang các thị trường mới.
+HR sẽ cập nhật mô tả công việc để phù hợp với cơ cấu mới.
+Chúng ta sẽ truyền thông rõ ràng những thay đổi này đến toàn thể nhân viên.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>What structure is the company moving toward?</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>A functional structure</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>No structure</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>A family structure</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>When will the structure be reviewed again?</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>In eighteen months</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Next week</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>30-Training</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Trao đổi về kế hoạch đào tạo</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>A: Could you tell me about our training plan for this year?
+B: Sure. We focus on three areas: onboarding, skills, and leadership.
+A: How long is the onboarding training for new employees?
+B: New employees complete a one-week onboarding program.
+A: What kind of skills training do you offer?
+B: We offer both technical training and soft skills workshops.
+A: How do employees register for a training course?
+B: They register through our internal learning platform.
+A: Is training mandatory for everyone?
+B: Onboarding is mandatory, but skills training is mostly optional.
+A: How do you measure the effectiveness of training?
+B: We collect feedback surveys and track performance improvement afterward.</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>A: Anh có thể cho tôi biết về kế hoạch đào tạo năm nay không?
+B: Được. Chúng tôi tập trung vào ba mảng: hội nhập, kỹ năng và lãnh đạo.
+A: Đào tạo hội nhập cho nhân viên mới kéo dài bao lâu?
+B: Nhân viên mới hoàn thành chương trình hội nhập kéo dài một tuần.
+A: Các anh cung cấp đào tạo kỹ năng gì?
+B: Chúng tôi cung cấp cả đào tạo chuyên môn và các buổi hội thảo kỹ năng mềm.
+A: Nhân viên đăng ký khóa đào tạo như thế nào?
+B: Họ đăng ký qua nền tảng học tập nội bộ của chúng tôi.
+A: Đào tạo có bắt buộc với tất cả mọi người không?
+B: Hội nhập là bắt buộc, nhưng đào tạo kỹ năng phần lớn là tự nguyện.
+A: Các anh đo lường hiệu quả đào tạo như thế nào?
+B: Chúng tôi thu thập khảo sát phản hồi và theo dõi sự cải thiện hiệu suất sau đó.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>How long is the onboarding program?</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>One day</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>One week</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>One month</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Is skills training mandatory?</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Yes, always</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Mostly optional</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Only for managers</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>